--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UNIVERSIDAD DE OVIEDO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UNIVERSIDAD DE OVIEDO.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>20.0611</v>
+        <v>19.9011</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2247</v>
+        <v>12.7377</v>
       </c>
       <c r="F2" t="n">
-        <v>7.836499999999999</v>
+        <v>7.1634</v>
       </c>
       <c r="G2" t="n">
-        <v>7.848000000000001</v>
+        <v>7.7898</v>
       </c>
       <c r="H2" t="n">
-        <v>6.0529</v>
+        <v>6.1193</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7951</v>
+        <v>1.6705</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1473</v>
+        <v>6.4618</v>
       </c>
       <c r="K2" t="n">
-        <v>6.3055</v>
+        <v>6.5993</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1581</v>
+        <v>-0.1377</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7007</v>
+        <v>1.3281</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2526</v>
+        <v>-0.4801</v>
       </c>
       <c r="O2" t="n">
-        <v>1.9533</v>
+        <v>1.8081</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.0017</v>
+        <v>-5.8421</v>
       </c>
       <c r="R2" t="n">
-        <v>5.0014</v>
+        <v>4.8684</v>
       </c>
       <c r="S2" t="n">
-        <v>8.0741</v>
+        <v>7.8696</v>
       </c>
       <c r="T2" t="n">
-        <v>7.1004</v>
+        <v>7.006</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9737</v>
+        <v>0.8636999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1392</v>
+        <v>5.2153</v>
       </c>
       <c r="W2" t="n">
-        <v>4.9786</v>
+        <v>5.112100000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1606</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.604799999999999</v>
+        <v>5.7714</v>
       </c>
       <c r="E3" t="n">
-        <v>4.745500000000001</v>
+        <v>5.459</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8593</v>
+        <v>0.3124</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1098</v>
+        <v>6.2224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1156</v>
+        <v>0.1124</v>
       </c>
       <c r="I3" t="n">
-        <v>5.994199999999999</v>
+        <v>6.109999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5211</v>
+        <v>7.9575</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2666</v>
+        <v>2.453</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2545</v>
+        <v>5.5045</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4113</v>
+        <v>-1.7352</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.151</v>
+        <v>-2.3406</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7397</v>
+        <v>0.6054999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6004</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.0017</v>
+        <v>-5.8421</v>
       </c>
       <c r="R3" t="n">
-        <v>4.4012</v>
+        <v>4.2842</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1043</v>
+        <v>-0.1142</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3070999999999999</v>
+        <v>0.3425</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4114</v>
+        <v>-0.4566</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9191</v>
+        <v>3.0011</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.561199999999999</v>
+        <v>4.521</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7957</v>
+        <v>3.9983</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7655000000000001</v>
+        <v>0.5227999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1467</v>
+        <v>5.1601</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5473</v>
+        <v>1.5127</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5995</v>
+        <v>3.6474</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3627</v>
+        <v>5.51</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3193</v>
+        <v>2.381</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0434</v>
+        <v>3.1289</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.216</v>
+        <v>-0.3498</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7721</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5562</v>
+        <v>0.5184</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8002</v>
+        <v>-0.779</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2004</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7343000000000001</v>
+        <v>0.6988</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4335</v>
+        <v>0.4356</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3008</v>
+        <v>0.2632</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4069</v>
+        <v>3.2923</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8945</v>
+        <v>-1.5877</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3014</v>
+        <v>4.88</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2851</v>
+        <v>1.2426</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3593</v>
+        <v>1.2504</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07429999999999998</v>
+        <v>-0.007800000000000029</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1031</v>
+        <v>0.1253000000000002</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6833999999999999</v>
+        <v>0.7646999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7866000000000001</v>
+        <v>-0.6394000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3882</v>
+        <v>1.1175</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6759000000000001</v>
+        <v>0.4857</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7122999999999999</v>
+        <v>0.6316999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0008</v>
+        <v>2.921</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>4.0011</v>
+        <v>3.8947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.879</v>
+        <v>-0.8714</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7911</v>
+        <v>-0.7393000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08789999999999998</v>
+        <v>-0.1322</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,31 +877,31 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3996</v>
+        <v>2.4316</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3147</v>
+        <v>1.3704</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04490000000000016</v>
+        <v>0.4024000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3596</v>
+        <v>0.968</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9932</v>
+        <v>2.0116</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6059999999999999</v>
+        <v>0.6600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3872</v>
+        <v>1.3517</v>
       </c>
       <c r="J7" t="n">
-        <v>3.153799999999999</v>
+        <v>3.4613</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3502</v>
+        <v>2.6019</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8037000000000001</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1606</v>
+        <v>-1.4497</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7442</v>
+        <v>-1.942</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5835</v>
+        <v>0.4923</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002000000000001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-2.9211</v>
       </c>
       <c r="R7" t="n">
-        <v>3.601</v>
+        <v>3.5052</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8786</v>
+        <v>-1.8359</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7978</v>
+        <v>-0.7484999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0808</v>
+        <v>-1.0875</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0575</v>
+        <v>-1.1706</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9411</v>
+        <v>1.0651</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9986</v>
+        <v>-2.2358</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5923</v>
+        <v>-0.673</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0128</v>
+        <v>-1.0586</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4205</v>
+        <v>0.3855999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4233</v>
+        <v>1.5136</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3014</v>
+        <v>1.3676</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1219</v>
+        <v>0.146</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0156</v>
+        <v>-2.1867</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.3142</v>
+        <v>-2.4263</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2986</v>
+        <v>0.2396</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6062</v>
+        <v>-1.555</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4822</v>
+        <v>-0.4485</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1239</v>
+        <v>-1.1064</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8932</v>
+        <v>-2.0025</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9432</v>
+        <v>-1.446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05000000000000004</v>
+        <v>-0.5565000000000002</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4498</v>
+        <v>1.3811</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1996</v>
+        <v>-1.2315</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6496</v>
+        <v>2.6127</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0542</v>
+        <v>3.3334</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6868</v>
+        <v>1.8578</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3674</v>
+        <v>1.4757</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6043</v>
+        <v>-1.9523</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8864</v>
+        <v>-3.0893</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2822</v>
+        <v>1.1371</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2000999999999999</v>
+        <v>0.1948</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0012</v>
+        <v>-3.8947</v>
       </c>
       <c r="R9" t="n">
-        <v>4.2012</v>
+        <v>4.0895</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1639</v>
+        <v>-2.1293</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.8559</v>
+        <v>-1.7747</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3080000000000001</v>
+        <v>-0.3546</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3793</v>
+        <v>-1.4489</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.239</v>
+        <v>-2.3389</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3046</v>
+        <v>-2.0907</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0645</v>
+        <v>-4.2825</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7598</v>
+        <v>2.1919</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2768</v>
+        <v>0.3481</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2222</v>
+        <v>1.2295</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9454</v>
+        <v>-0.8813999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2677</v>
+        <v>0.6872</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8103</v>
+        <v>2.0478</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5427</v>
+        <v>-1.3606</v>
       </c>
       <c r="M10" t="n">
-        <v>0.009100000000000011</v>
+        <v>-0.3391</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5881</v>
+        <v>-0.8182</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5972</v>
+        <v>0.4791</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.002000000000001</v>
+        <v>-6.8157</v>
       </c>
       <c r="R10" t="n">
-        <v>4.6013</v>
+        <v>4.4789</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9001</v>
+        <v>-1.882</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.8492</v>
+        <v>-1.7655</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0509</v>
+        <v>-0.1164999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="W10" t="n">
-        <v>3.519</v>
+        <v>3.6116</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>C. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4677</v>
+        <v>-2.4445</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0735</v>
+        <v>-2.8346</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3942</v>
+        <v>0.39</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9812999999999998</v>
+        <v>-1.8109</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.183</v>
+        <v>-2.0767</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2018</v>
+        <v>0.2658</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4273</v>
+        <v>-1.9319</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2599</v>
+        <v>-1.9319</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1674</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4086</v>
+        <v>0.1211</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4429</v>
+        <v>-0.1447</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0343</v>
+        <v>0.2658</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4001</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4007</v>
+        <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2267</v>
+        <v>0.1453</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1602</v>
+        <v>0.0711</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0664</v>
+        <v>0.0742</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3401</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. MARTINEZ FERNANDEZ</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4832</v>
+        <v>-2.5133</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9032</v>
+        <v>-1.8516</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4199</v>
+        <v>-0.6617</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8315</v>
+        <v>-1.0639</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1027</v>
+        <v>-2.3042</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2712</v>
+        <v>1.2402</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.974</v>
+        <v>1.5398</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.974</v>
+        <v>0.2668</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1425</v>
+        <v>-2.6038</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1287</v>
+        <v>-2.571</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2712</v>
+        <v>-0.0328</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2001</v>
+        <v>2.3369</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1485</v>
+        <v>-2.1699</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0711</v>
+        <v>-1.113</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.0568</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.705</v>
+        <v>-3.6643</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9199</v>
+        <v>-4.7407</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2149</v>
+        <v>1.0763</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8334</v>
+        <v>-1.8406</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1466</v>
+        <v>-1.1582</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6867</v>
+        <v>-0.6824</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2103</v>
+        <v>-2.1131</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9056</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.236</v>
+        <v>-1.2075</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3769</v>
+        <v>0.2725</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1723</v>
+        <v>-0.2526</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5493</v>
+        <v>0.5249999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6004</v>
+        <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4715</v>
+        <v>-1.4342</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.709</v>
+        <v>-0.6801999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7625</v>
+        <v>-0.7541</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.9237</v>
+        <v>-6.9293</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.2348</v>
+        <v>-6.6648</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3110999999999999</v>
+        <v>-0.2645</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9320999999999999</v>
+        <v>0.8674999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5222</v>
+        <v>1.5374</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.59</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2723</v>
+        <v>1.5212</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8664</v>
+        <v>3.0689</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.594</v>
+        <v>-1.5477</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3403</v>
+        <v>-0.6536</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3443</v>
+        <v>-1.5315</v>
       </c>
       <c r="O14" t="n">
-        <v>1.004</v>
+        <v>0.8778</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.2015</v>
+        <v>-5.0632</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.002599999999999</v>
+        <v>-8.7631</v>
       </c>
       <c r="R14" t="n">
-        <v>3.8011</v>
+        <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0.004999999999999998</v>
+        <v>-0.0121</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3642000000000001</v>
+        <v>-0.3129</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3693000000000001</v>
+        <v>0.3007</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8596999999999999</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.519</v>
+        <v>-3.6116</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>16.51339999999999</v>
+        <v>16.4726</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.971900000000002</v>
+        <v>2.686199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>18.4852</v>
+        <v>13.7863</v>
       </c>
       <c r="G15" t="n">
-        <v>22.2026</v>
+        <v>22.0664</v>
       </c>
       <c r="H15" t="n">
-        <v>4.780799999999999</v>
+        <v>4.5925</v>
       </c>
       <c r="I15" t="n">
-        <v>17.4223</v>
+        <v>17.474</v>
       </c>
       <c r="J15" t="n">
-        <v>27.7419</v>
+        <v>30.4977</v>
       </c>
       <c r="K15" t="n">
-        <v>18.9015</v>
+        <v>20.5713</v>
       </c>
       <c r="L15" t="n">
-        <v>8.8405</v>
+        <v>9.9262</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.5393</v>
+        <v>-8.431000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.1209</v>
+        <v>-15.979</v>
       </c>
       <c r="O15" t="n">
-        <v>8.581799999999999</v>
+        <v>7.547599999999998</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.001600000000001</v>
+        <v>-5.8421</v>
       </c>
       <c r="Q15" t="n">
-        <v>-43.0125</v>
+        <v>-41.8684</v>
       </c>
       <c r="R15" t="n">
-        <v>37.0105</v>
+        <v>36.0262</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.268400000000001</v>
+        <v>-3.2903</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.09749999999999914</v>
+        <v>0.2726000000000004</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.1707</v>
+        <v>-3.5629</v>
       </c>
       <c r="V15" t="n">
-        <v>3.5805</v>
+        <v>3.5385</v>
       </c>
       <c r="W15" t="n">
-        <v>13.3959</v>
+        <v>13.7842</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.8156</v>
+        <v>-10.2459</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UNIVERSIDAD DE OVIEDO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_UNIVERSIDAD DE OVIEDO.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>19.9011</v>
+        <v>14.8599</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7377</v>
+        <v>8.0151</v>
       </c>
       <c r="F2" t="n">
-        <v>7.1634</v>
+        <v>6.8448</v>
       </c>
       <c r="G2" t="n">
         <v>7.7898</v>
@@ -610,13 +610,13 @@
         <v>4.8684</v>
       </c>
       <c r="S2" t="n">
-        <v>7.8696</v>
+        <v>2.8285</v>
       </c>
       <c r="T2" t="n">
-        <v>7.006</v>
+        <v>2.2834</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8636999999999999</v>
+        <v>0.5450999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>5.2153</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7714</v>
+        <v>5.4722</v>
       </c>
       <c r="E3" t="n">
-        <v>5.459</v>
+        <v>5.2217</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3124</v>
+        <v>0.2504999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>6.2224</v>
@@ -688,13 +688,13 @@
         <v>4.2842</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1142</v>
+        <v>-0.4132</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3425</v>
+        <v>0.1052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4566</v>
+        <v>-0.5185</v>
       </c>
       <c r="V3" t="n">
         <v>1.2211</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.521</v>
+        <v>4.7064</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9983</v>
+        <v>-0.5291000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5227999999999999</v>
+        <v>5.2354</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1601</v>
+        <v>1.2426</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5127</v>
+        <v>1.2504</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6474</v>
+        <v>-0.007800000000000029</v>
       </c>
       <c r="J4" t="n">
-        <v>5.51</v>
+        <v>0.1253000000000002</v>
       </c>
       <c r="K4" t="n">
-        <v>2.381</v>
+        <v>0.7646999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1289</v>
+        <v>-0.6394000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3498</v>
+        <v>1.1175</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8683999999999999</v>
+        <v>0.4857</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5184</v>
+        <v>0.6316999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.779</v>
+        <v>2.921</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1684</v>
+        <v>3.8947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6988</v>
+        <v>0.5427</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4356</v>
+        <v>0.3193</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2632</v>
+        <v>0.2234</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2923</v>
+        <v>4.2984</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5877</v>
+        <v>3.9982</v>
       </c>
       <c r="F5" t="n">
-        <v>4.88</v>
+        <v>0.3002</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2426</v>
+        <v>5.1601</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2504</v>
+        <v>1.5127</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.007800000000000029</v>
+        <v>3.6474</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1253000000000002</v>
+        <v>5.51</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7646999999999999</v>
+        <v>2.381</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6394000000000001</v>
+        <v>3.1289</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1175</v>
+        <v>-0.3498</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4857</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6316999999999999</v>
+        <v>0.5184</v>
       </c>
       <c r="P5" t="n">
-        <v>2.921</v>
+        <v>-0.779</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R5" t="n">
-        <v>3.8947</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8714</v>
+        <v>0.4763000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7393000000000001</v>
+        <v>0.4356</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1322</v>
+        <v>0.0405</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4316</v>
+        <v>2.5365</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4316</v>
+        <v>0.9626000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.574</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4316</v>
+        <v>2.0116</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.6600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4316</v>
+        <v>1.3517</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4316</v>
+        <v>3.4613</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.6019</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4316</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.4497</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.942</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.4923</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9211</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.5052</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.6698</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1883</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.4816</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3704</v>
+        <v>2.4316</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4024000000000001</v>
+        <v>2.4316</v>
       </c>
       <c r="F7" t="n">
-        <v>0.968</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0116</v>
+        <v>2.4316</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3517</v>
+        <v>2.4316</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4613</v>
+        <v>2.4316</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6019</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8593999999999999</v>
+        <v>2.4316</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4497</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.942</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4923</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9211</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.5052</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8359</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7484999999999999</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEREZ REQUENA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1706</v>
+        <v>-0.6737000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0651</v>
+        <v>-2.8253</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2358</v>
+        <v>2.1516</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.673</v>
+        <v>0.3481</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0586</v>
+        <v>1.2295</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3855999999999999</v>
+        <v>-0.8813999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5136</v>
+        <v>0.6872</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3676</v>
+        <v>2.0478</v>
       </c>
       <c r="L8" t="n">
-        <v>0.146</v>
+        <v>-1.3606</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1867</v>
+        <v>-0.3391</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4263</v>
+        <v>-0.8182</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2396</v>
+        <v>0.4791</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9474</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-6.8157</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9474</v>
+        <v>4.4789</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.555</v>
+        <v>-0.465</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4485</v>
+        <v>-0.3082</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1064</v>
+        <v>-0.1567</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.89</v>
+        <v>1.78</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.6116</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.89</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0025</v>
+        <v>-0.8287000000000004</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.446</v>
+        <v>-0.3496000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5565000000000002</v>
+        <v>-0.4791</v>
       </c>
       <c r="G9" t="n">
         <v>1.3811</v>
@@ -1156,13 +1156,13 @@
         <v>4.0895</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1293</v>
+        <v>-0.9557</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7747</v>
+        <v>-0.6783</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3546</v>
+        <v>-0.2774</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4489</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>A. PEREZ REQUENA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0907</v>
+        <v>-0.9364</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2825</v>
+        <v>0.9655</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1919</v>
+        <v>-1.9019</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3481</v>
+        <v>-0.673</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2295</v>
+        <v>-1.0586</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8813999999999999</v>
+        <v>0.3855999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6872</v>
+        <v>1.5136</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0478</v>
+        <v>1.3676</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3606</v>
+        <v>0.146</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3391</v>
+        <v>-2.1867</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8182</v>
+        <v>-2.4263</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4791</v>
+        <v>0.2396</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3368</v>
+        <v>1.9474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.8157</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.4789</v>
+        <v>1.9474</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.882</v>
+        <v>-1.3207</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7655</v>
+        <v>-0.5482</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1164999999999999</v>
+        <v>-0.7725</v>
       </c>
       <c r="V10" t="n">
-        <v>1.78</v>
+        <v>-0.89</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6116</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8316</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MARTINEZ FERNANDEZ</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4445</v>
+        <v>-1.6648</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8346</v>
+        <v>-1.2535</v>
       </c>
       <c r="F11" t="n">
-        <v>0.39</v>
+        <v>-0.4113</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8109</v>
+        <v>-1.0639</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0767</v>
+        <v>-2.3042</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2658</v>
+        <v>1.2402</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9319</v>
+        <v>1.5398</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9319</v>
+        <v>0.2668</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.273</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1211</v>
+        <v>-2.6038</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1447</v>
+        <v>-2.571</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2658</v>
+        <v>-0.0328</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1947</v>
+        <v>2.3369</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1453</v>
+        <v>-1.3214</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0711</v>
+        <v>-0.5149</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0742</v>
+        <v>-0.8065</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>C. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5133</v>
+        <v>-2.2336</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8516</v>
+        <v>-2.7349</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6617</v>
+        <v>0.5013</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0639</v>
+        <v>-1.8109</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3042</v>
+        <v>-2.0767</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2402</v>
+        <v>0.2658</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5398</v>
+        <v>-1.9319</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2668</v>
+        <v>-1.9319</v>
       </c>
       <c r="L12" t="n">
-        <v>1.273</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6038</v>
+        <v>0.1211</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.571</v>
+        <v>-0.1447</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0328</v>
+        <v>0.2658</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3895</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3369</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1699</v>
+        <v>0.3562</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.113</v>
+        <v>0.1707</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0568</v>
+        <v>0.1855</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3311</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3311</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6643</v>
+        <v>-2.9541</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7407</v>
+        <v>-4.4416</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0763</v>
+        <v>1.4875</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8406</v>
@@ -1468,13 +1468,13 @@
         <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4342</v>
+        <v>-0.7241</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6801999999999999</v>
+        <v>-0.3812</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7541</v>
+        <v>-0.3429</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.9293</v>
+        <v>-6.9032</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.6648</v>
+        <v>-6.4655</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2645</v>
+        <v>-0.4376</v>
       </c>
       <c r="G14" t="n">
         <v>0.8674999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0121</v>
+        <v>0.0141</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3129</v>
+        <v>-0.1134999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3007</v>
+        <v>0.1275000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7216</v>
@@ -1579,13 +1579,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>16.4726</v>
+        <v>18.1105</v>
       </c>
       <c r="E15" t="n">
-        <v>2.686199999999999</v>
+        <v>2.9952</v>
       </c>
       <c r="F15" t="n">
-        <v>13.7863</v>
+        <v>15.1154</v>
       </c>
       <c r="G15" t="n">
         <v>22.0664</v>
@@ -1597,7 +1597,7 @@
         <v>17.474</v>
       </c>
       <c r="J15" t="n">
-        <v>30.4977</v>
+        <v>30.49770000000001</v>
       </c>
       <c r="K15" t="n">
         <v>20.5713</v>
@@ -1606,13 +1606,13 @@
         <v>9.9262</v>
       </c>
       <c r="M15" t="n">
-        <v>-8.431000000000001</v>
+        <v>-8.430999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-15.979</v>
       </c>
       <c r="O15" t="n">
-        <v>7.547599999999998</v>
+        <v>7.5476</v>
       </c>
       <c r="P15" t="n">
         <v>-5.8421</v>
@@ -1624,13 +1624,13 @@
         <v>36.0262</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.2903</v>
+        <v>-1.6521</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2726000000000004</v>
+        <v>0.5816000000000003</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.5629</v>
+        <v>-2.2341</v>
       </c>
       <c r="V15" t="n">
         <v>3.5385</v>
